--- a/apps/web/public/templates/roster-bulk-import-template.xlsx
+++ b/apps/web/public/templates/roster-bulk-import-template.xlsx
@@ -4,16 +4,221 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Classes" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Subjects" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Teacher Assignments" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Classes" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Subjects" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Teacher Assignments" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Required. The class label as it should appear everywhere, e.g. "JSS 1A".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Required. The grade band this class belongs to, e.g. "JSS1", "SS2", "Primary 4".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Optional. A subject-track subdivision within a class, e.g. "Science", "Arts", "Commercial". Leave blank if your school does not stream classes. See the Instructions sheet for examples.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>Optional. Email of an existing staff account to set as this class's form teacher. Leave blank to assign later.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Required. The subject's full name, e.g. "Mathematics".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Required. A short subject code, e.g. "MATH". Used to reference this subject in the Teacher Assignments sheet.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Required. Email of an existing staff account with the teacher role.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Required. Must exactly match a "Name" from the Classes sheet.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Required. Must exactly match a "Code" from the Subjects sheet.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
+  <si>
+    <t>Chronix Edu — Roster Bulk Import</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>This workbook has 3 data sheets: Classes, Subjects, Teacher Assignments.</t>
+  </si>
+  <si>
+    <t>Fill them in, then upload this file. Do not rename the sheet tabs.</t>
+  </si>
+  <si>
+    <t>Import order matters: Classes and Subjects must exist before Teacher Assignments can reference them.</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>What it means</t>
+  </si>
+  <si>
+    <t>Classes</t>
+  </si>
+  <si>
+    <t>Name (required)</t>
+  </si>
+  <si>
+    <t>The class label as you want it to appear everywhere, e.g. "JSS 1A".</t>
+  </si>
+  <si>
+    <t>Level (required)</t>
+  </si>
+  <si>
+    <t>The grade band this class belongs to, e.g. "JSS1", "SS2", "Primary 4". Used to group classes for grading/reporting.</t>
+  </si>
+  <si>
+    <t>Stream (optional)</t>
+  </si>
+  <si>
+    <t>A subject-track subdivision within a class, e.g. "Science", "Arts", "Commercial" — for schools that split students by track. Leave blank if your school does not stream classes.</t>
+  </si>
+  <si>
+    <t>Form Teacher Email (optional)</t>
+  </si>
+  <si>
+    <t>The email of the staff account to set as this class's form teacher. Must already exist as a staff account — leave blank to assign later.</t>
+  </si>
+  <si>
+    <t>Subjects</t>
+  </si>
+  <si>
+    <t>The subject's full name, e.g. "Mathematics".</t>
+  </si>
+  <si>
+    <t>Code (required)</t>
+  </si>
+  <si>
+    <t>A short subject code, e.g. "MATH". Used to reference this subject in Teacher Assignments below.</t>
+  </si>
+  <si>
+    <t>Teacher Assignments</t>
+  </si>
+  <si>
+    <t>Teacher Email (required)</t>
+  </si>
+  <si>
+    <t>The email of an existing staff account with the teacher role.</t>
+  </si>
+  <si>
+    <t>Class Name (required)</t>
+  </si>
+  <si>
+    <t>Must exactly match a "Name" from the Classes sheet (in this file, or already in the system).</t>
+  </si>
+  <si>
+    <t>Subject Code (required)</t>
+  </si>
+  <si>
+    <t>Must exactly match a "Code" from the Subjects sheet (in this file, or already in the system).</t>
+  </si>
+  <si>
+    <t>Worked example</t>
+  </si>
+  <si>
+    <t>Classes:</t>
+  </si>
+  <si>
+    <t>Name=JSS 1A, Level=JSS1, Stream=(blank), Form Teacher Email=(blank)</t>
+  </si>
+  <si>
+    <t>Classes (streamed school):</t>
+  </si>
+  <si>
+    <t>Name=SS 2 Science, Level=SS2, Stream=Science</t>
+  </si>
+  <si>
+    <t>Subjects:</t>
+  </si>
+  <si>
+    <t>Name=Mathematics, Code=MATH</t>
+  </si>
+  <si>
+    <t>Teacher Assignments:</t>
+  </si>
+  <si>
+    <t>Teacher Email=jane@school.com, Class Name=JSS 1A, Subject Code=MATH</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
@@ -27,21 +232,9 @@
     <t>Form Teacher Email</t>
   </si>
   <si>
-    <t>EXAMPLE-DELETE-THIS-ROW</t>
-  </si>
-  <si>
-    <t>JSS1</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>DEL</t>
-  </si>
-  <si>
     <t>Teacher Email</t>
   </si>
   <si>
@@ -49,16 +242,13 @@
   </si>
   <si>
     <t>Subject Code</t>
-  </si>
-  <si>
-    <t>delete-this-example-row@example.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -68,20 +258,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF003366"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -96,9 +284,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,15 +630,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,24 +646,238 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -482,69 +888,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>